--- a/data/trans_orig/P21D3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44777</t>
+          <t>44265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71351</t>
+          <t>69765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78568</t>
+          <t>80083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>111697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158166</t>
+          <t>159025</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184556</t>
+          <t>185056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282609</t>
+          <t>282111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302776</t>
+          <t>302579</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448057</t>
+          <t>448191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483027</t>
+          <t>480988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,47 +1006,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>6346</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>11685</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>6346</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1246</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1246</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3880</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138729</t>
+          <t>142084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>355562</t>
+          <t>351801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200761</t>
+          <t>201811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>405921</t>
+          <t>428765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378578</t>
+          <t>366942</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>667954</t>
+          <t>674245</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>756795</t>
+          <t>760626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>976947</t>
+          <t>972135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>525487</t>
+          <t>499984</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>727929</t>
+          <t>726732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1375327</t>
+          <t>1368255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1667926</t>
+          <t>1679010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62910</t>
+          <t>62052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97346</t>
+          <t>96384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60553</t>
+          <t>59566</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>86958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129101</t>
+          <t>129812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175112</t>
+          <t>172920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>209895</t>
+          <t>210803</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>244853</t>
+          <t>245832</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>222424</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>249022</t>
+          <t>249642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>442219</t>
+          <t>442014</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>488062</t>
+          <t>486069</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>239638</t>
+          <t>250792</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>485921</t>
+          <t>487329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>312567</t>
+          <t>309419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>556046</t>
+          <t>562491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>622752</t>
+          <t>602671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>927320</t>
+          <t>920388</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1162895</t>
+          <t>1161828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1410635</t>
+          <t>1400409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1021967</t>
+          <t>1011356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1257933</t>
+          <t>1262120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2296537</t>
+          <t>2299363</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2605599</t>
+          <t>2623291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">

--- a/data/trans_orig/P21D3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>72191</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44265</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69765</t>
+          <t>89396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30188</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>53983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>94988</t>
+          <t>114810</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>98072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111697</t>
+          <t>137678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>172925</t>
+          <t>179639</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>159025</t>
+          <t>162797</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185056</t>
+          <t>194066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>293306</t>
+          <t>315605</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282111</t>
+          <t>303770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302579</t>
+          <t>326039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>466231</t>
+          <t>495244</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>448191</t>
+          <t>472592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>480988</t>
+          <t>513075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>253655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>364366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>568811</t>
+          <t>618021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>265504</t>
+          <t>304478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>142084</t>
+          <t>266808</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>351801</t>
+          <t>339395</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>263480</t>
+          <t>223259</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>201811</t>
+          <t>197863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>428765</t>
+          <t>250769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>528984</t>
+          <t>527737</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>366942</t>
+          <t>484277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>674245</t>
+          <t>576957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>847809</t>
+          <t>650985</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>760626</t>
+          <t>616298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>972135</t>
+          <t>689496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>665881</t>
+          <t>753761</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499984</t>
+          <t>722889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>726732</t>
+          <t>778571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1513689</t>
+          <t>1404747</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1368255</t>
+          <t>1356186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1679010</t>
+          <t>1448002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>800</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>16212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10241</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1117133</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>937313</t>
+          <t>985519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2054446</t>
+          <t>1945029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>79265</t>
+          <t>90985</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62052</t>
+          <t>73719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96384</t>
+          <t>112937</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72606</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>65412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>94793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>151871</t>
+          <t>168969</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>146832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172920</t>
+          <t>194505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>228307</t>
+          <t>253609</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>210803</t>
+          <t>231136</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>245832</t>
+          <t>270941</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>236387</t>
+          <t>260701</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>221928</t>
+          <t>244300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>249642</t>
+          <t>273095</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>464695</t>
+          <t>514309</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>442014</t>
+          <t>489383</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>486069</t>
+          <t>537091</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>310183</t>
+          <t>347209</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>312287</t>
+          <t>342240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622471</t>
+          <t>689448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>400885</t>
+          <t>467654</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>250792</t>
+          <t>427240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>487329</t>
+          <t>509786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>374957</t>
+          <t>343862</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>309419</t>
+          <t>311448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>562491</t>
+          <t>375969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>775842</t>
+          <t>811516</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>602671</t>
+          <t>757852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>920388</t>
+          <t>868033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1249041</t>
+          <t>1084233</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1161828</t>
+          <t>1042541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1400409</t>
+          <t>1127742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1195573</t>
+          <t>1330067</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1011356</t>
+          <t>1297252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1262120</t>
+          <t>1362964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2444615</t>
+          <t>2414300</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2299363</t>
+          <t>2355989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2623291</t>
+          <t>2467237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>34854</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1658193</t>
+          <t>1560374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1587534</t>
+          <t>1692124</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3245727</t>
+          <t>3252498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
